--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,353 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115114935</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95833</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>307023</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6463080</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115114931</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95550</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blockskapania</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scapania gracilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>307023</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6463080</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>stereolupp</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115115088</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Myren, 100 m NNO om, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>306940</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6462949</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>OB-Oru-0109</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterad på ett halvdussin ställen. men fler kan finnas.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -795,11 +795,11 @@
         <v>115115088</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>115115088</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104122685</v>
+        <v>115114931</v>
       </c>
       <c r="B2" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2666</v>
+        <v>1454</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Scapania gracilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307022.5674844779</v>
+        <v>307022</v>
       </c>
       <c r="R2" t="n">
-        <v>6463079.832452034</v>
+        <v>6463080</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,13 +758,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>stereolupp</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>i nedre delen av hög brant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,62 +781,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115115088</v>
+        <v>115114935</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myren, 100 m NNO om, Boh</t>
+          <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306940</v>
+        <v>307022</v>
       </c>
       <c r="R3" t="n">
-        <v>6462950</v>
+        <v>6463080</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,11 +848,6 @@
           <t>Torp</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OB-Oru-0109</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2024-03-09</t>
@@ -885,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Noterad på ett halvdussin ställen. men fler kan finnas.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,52 +879,39 @@
           <t>Olle Molander</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115114931</v>
+        <v>104122685</v>
       </c>
       <c r="B4" t="n">
-        <v>95640</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1454</v>
+        <v>2666</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scapania gracilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
@@ -995,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,13 +962,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>stereolupp</t>
-        </is>
-      </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i nedre delen av hög brant</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,54 +985,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115114935</v>
+        <v>115115088</v>
       </c>
       <c r="B5" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyrs vatten, 75 m SSV om S-änden, Boh</t>
+          <t>Myren, 100 m NNO om, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>307022</v>
+        <v>306940</v>
       </c>
       <c r="R5" t="n">
-        <v>6463080</v>
+        <v>6462950</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,6 +1060,11 @@
           <t>Torp</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>OB-Oru-0109</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2024-03-09</t>
@@ -1112,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterad på ett halvdussin ställen. men fler kan finnas.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1101,11 @@
           <t>Olle Molander</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65099-2023 artfynd.xlsx
+++ b/artfynd/A 65099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115114931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115114935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104122685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,8 +1126,19 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115115088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>